--- a/index.xlsx
+++ b/index.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Il mio Drive\Progetti\ntJobsAI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Il mio Drive\Progetti\ntJobsAi2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F827A3D-B18D-4078-971E-F3B22712AD5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33D10675-937D-4C7F-9949-EBA0589287E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="files" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="history" sheetId="3" r:id="rId3"/>
     <sheet name="legend" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="CalcA1ExcelA1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="83">
   <si>
     <t>NAME</t>
   </si>
@@ -102,9 +102,6 @@
     <t>DATA</t>
   </si>
   <si>
-    <t>*W Funzioni/Classi di Interfaccia di un modulo FrontEnd (App) verso ntJobsOS. Lettura Input, Scrittura Ritorno</t>
-  </si>
-  <si>
     <t>T</t>
   </si>
   <si>
@@ -189,60 +186,18 @@
     <t>Deprecata</t>
   </si>
   <si>
-    <t xml:space="preserve">acJobsApp.py   </t>
-  </si>
-  <si>
-    <t>aiSys.py</t>
-  </si>
-  <si>
-    <t>Funzioni e Classi Core di tutto ecosistema aiJobs</t>
-  </si>
-  <si>
     <t>ntjobs_app_man_XX.pdf</t>
   </si>
   <si>
     <t>Manual/Manuale ntJobsApp it/en</t>
   </si>
   <si>
-    <t>Prompt_ntJobsApp.docx</t>
-  </si>
-  <si>
-    <t>Prompt generazione ntJobsApp (Open)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">aiobsOS.py      </t>
-  </si>
-  <si>
-    <t>ntj_admin.py</t>
-  </si>
-  <si>
-    <t>Comandi Vari Generici di Amministrazione</t>
-  </si>
-  <si>
-    <t>ntj_admin.cmd</t>
-  </si>
-  <si>
-    <t>admin_mirror_k.cmd</t>
-  </si>
-  <si>
-    <t>admin_mirror_git.cmd</t>
-  </si>
-  <si>
-    <t>Mirror su K: Kit aiJobs</t>
-  </si>
-  <si>
-    <t>Mirror per GITHUB: Kit aiJobs</t>
-  </si>
-  <si>
     <t>ntjobs_config.ini</t>
   </si>
   <si>
     <t>Inbox</t>
   </si>
   <si>
-    <t>APP.CMD</t>
-  </si>
-  <si>
     <t>Config Dati per NTJOBSOS</t>
   </si>
   <si>
@@ -267,83 +222,68 @@
     <t>Jobs Archiviati</t>
   </si>
   <si>
-    <t>aiJobsTest.py</t>
-  </si>
-  <si>
-    <t>Funzioni e Classi di supporto a ntJobsOS che si appoggiano a jData per  funzioni di Test</t>
-  </si>
-  <si>
-    <t>aiSysBase.py</t>
-  </si>
-  <si>
-    <t>aiSysFileio.py</t>
-  </si>
-  <si>
-    <t>aiSysConfig.py</t>
-  </si>
-  <si>
-    <t>aiSysStrings.py</t>
-  </si>
-  <si>
-    <t>aiSysTimestamp.py</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ncDictToString.py</t>
-  </si>
-  <si>
-    <t>ncMailSimple.py</t>
-  </si>
-  <si>
-    <t>Classe invio mail SMPT</t>
-  </si>
-  <si>
-    <t>Da Dizionario a Stringa json, xml</t>
-  </si>
-  <si>
-    <t>Gestione Timestamp</t>
-  </si>
-  <si>
-    <t>Gestione Dizionario Config</t>
-  </si>
-  <si>
-    <t>Stringhe</t>
-  </si>
-  <si>
-    <t>File Io</t>
-  </si>
-  <si>
-    <t>Dizionari e funzioni base</t>
-  </si>
-  <si>
-    <t>admin_pytest.cmd</t>
-  </si>
-  <si>
-    <t>Esecuione test</t>
-  </si>
-  <si>
     <t>ntjobs_billing.csv</t>
   </si>
   <si>
     <t>Biling file di esecuzione jobs</t>
   </si>
   <si>
-    <t xml:space="preserve">acJobsOS.py   </t>
-  </si>
-  <si>
-    <t>Classe principale acJobsOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">aiobsJobsJobs.py      </t>
-  </si>
-  <si>
-    <t>SubClasse JobsOS.Jobs</t>
+    <t xml:space="preserve">aiobsOS2.py      </t>
+  </si>
+  <si>
+    <t>Users</t>
+  </si>
+  <si>
+    <t>Inbox Singoli Users</t>
+  </si>
+  <si>
+    <t>Log</t>
+  </si>
+  <si>
+    <t>Temp</t>
+  </si>
+  <si>
+    <t>Log Folder</t>
+  </si>
+  <si>
+    <t>Temp zone</t>
+  </si>
+  <si>
+    <t>ntJobsApp</t>
+  </si>
+  <si>
+    <t>Kit per creare ntjobsApp, Python e VBA</t>
+  </si>
+  <si>
+    <t>ntjobsos.sh</t>
+  </si>
+  <si>
+    <t>ntjobsos.cmd</t>
+  </si>
+  <si>
+    <t>Script lancio ntjobsos bash linux</t>
+  </si>
+  <si>
+    <t>Script lancio ntjobsos windows command</t>
+  </si>
+  <si>
+    <t>admin_folders.sh</t>
+  </si>
+  <si>
+    <t>admin_folders.cmd</t>
+  </si>
+  <si>
+    <t>Creazione Folders CMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Creazione Folders BASH </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -376,25 +316,6 @@
       <color rgb="FFC9211E"/>
       <name val="Calibri"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFC9211E"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="5">
@@ -435,7 +356,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -457,13 +378,6 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -736,7 +650,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K1048508"/>
+  <dimension ref="A1:K1048490"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.28515625" style="1" customWidth="1"/>
@@ -753,43 +667,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="C1" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="18" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="18" t="s">
+      <c r="D1" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="18" t="s">
+      <c r="F1" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="19" t="s">
+      <c r="G1" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="18" t="s">
+      <c r="H1" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="20" t="s">
+      <c r="I1" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="16" t="s">
+      <c r="J1" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="20" t="s">
+      <c r="K1" s="17" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="B2" s="8" t="s">
         <v>11</v>
@@ -813,59 +727,56 @@
         <v>3</v>
       </c>
       <c r="I2" s="9">
-        <v>46029</v>
+        <v>46116</v>
       </c>
       <c r="J2" s="5" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="C3" s="6">
+      <c r="A3" s="7"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="6"/>
+      <c r="I3" s="9"/>
+    </row>
+    <row r="4" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="C4" s="3">
         <v>1</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I3" s="9">
-        <v>46029</v>
-      </c>
-      <c r="J3" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="7"/>
-      <c r="B4" s="8"/>
-      <c r="C4" s="6"/>
-      <c r="I4" s="9"/>
+      <c r="D4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I4" s="9">
+        <v>46116</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="5" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>57</v>
+        <v>19</v>
       </c>
       <c r="C5" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>3</v>
@@ -876,22 +787,25 @@
       <c r="F5" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="G5" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="H5" s="3" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="I5" s="9">
-        <v>46029</v>
+        <v>46116</v>
       </c>
       <c r="J5" s="5" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>19</v>
+        <v>54</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>56</v>
       </c>
       <c r="C6" s="3">
         <v>10</v>
@@ -900,39 +814,39 @@
         <v>3</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>3</v>
       </c>
       <c r="I6" s="9">
-        <v>46029</v>
+        <v>46116</v>
       </c>
       <c r="J6" s="5" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" s="6">
-        <v>2</v>
+        <v>57</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C7" s="3">
+        <v>1</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>13</v>
@@ -944,27 +858,27 @@
         <v>3</v>
       </c>
       <c r="I7" s="9">
-        <v>46029</v>
+        <v>46116</v>
       </c>
       <c r="J7" s="5" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="C8" s="6">
-        <v>2</v>
+        <v>59</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C8" s="3">
+        <v>10</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>13</v>
@@ -976,215 +890,219 @@
         <v>3</v>
       </c>
       <c r="I8" s="9">
-        <v>46059</v>
+        <v>46116</v>
       </c>
       <c r="J8" s="5" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C9" s="3">
+        <v>10</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I9" s="9">
+        <v>46116</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C10" s="3">
+        <v>10</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I10" s="9">
+        <v>46116</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C11" s="3">
+        <v>10</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I11" s="9">
+        <v>46116</v>
+      </c>
+      <c r="J11" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B9" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="C9" s="6">
-        <v>1</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I9" s="9"/>
-      <c r="J9" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
+      <c r="B12" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="B10" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="C10" s="6">
-        <v>1</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E10" s="3" t="s">
+      <c r="C12" s="3">
+        <v>10</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I12" s="9">
+        <v>46116</v>
+      </c>
+      <c r="J12" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C13" s="3">
+        <v>10</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I13" s="9">
+        <v>46116</v>
+      </c>
+      <c r="J13" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C14" s="3">
+        <v>10</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I14" s="9">
+        <v>46116</v>
+      </c>
+      <c r="J14" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="F10" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I10" s="9"/>
-      <c r="J10" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="C11" s="6">
-        <v>1</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I11" s="9">
-        <v>46047</v>
-      </c>
-      <c r="J11" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="C12" s="6">
-        <v>1</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I12" s="9">
-        <v>46047</v>
-      </c>
-      <c r="J12" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="C13" s="6">
-        <v>1</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I13" s="9">
-        <v>46047</v>
-      </c>
-      <c r="J13" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="C14" s="6">
-        <v>1</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I14" s="9">
-        <v>46047</v>
-      </c>
-      <c r="J14" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="C15" s="6">
-        <v>1</v>
+      <c r="B15" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C15" s="3">
+        <v>10</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>13</v>
@@ -1193,30 +1111,30 @@
         <v>13</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="I15" s="9">
-        <v>46047</v>
+        <v>46116</v>
       </c>
       <c r="J15" s="5" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="C16" s="6">
-        <v>1</v>
+        <v>73</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C16" s="3">
+        <v>10</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>13</v>
@@ -1225,30 +1143,30 @@
         <v>13</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="I16" s="9">
-        <v>46047</v>
+        <v>46116</v>
       </c>
       <c r="J16" s="5" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>87</v>
+      <c r="A17" s="7" t="s">
+        <v>75</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="C17" s="6">
         <v>1</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>13</v>
@@ -1260,27 +1178,27 @@
         <v>3</v>
       </c>
       <c r="I17" s="9">
-        <v>46047</v>
+        <v>46116</v>
       </c>
       <c r="J17" s="5" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>86</v>
+      <c r="A18" s="7" t="s">
+        <v>76</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="C18" s="6">
         <v>1</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>13</v>
@@ -1292,395 +1210,78 @@
         <v>3</v>
       </c>
       <c r="I18" s="9">
-        <v>46047</v>
+        <v>46116</v>
       </c>
       <c r="J18" s="5" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="B19" s="8" t="s">
+      <c r="B19" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C19" s="3">
+        <v>10</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I19" s="9">
+        <v>46116</v>
+      </c>
+      <c r="J19" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="C19" s="6">
-        <v>1</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I19" s="9">
-        <v>46031</v>
-      </c>
-      <c r="J19" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="B20" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="C20" s="6">
-        <v>1</v>
-      </c>
-      <c r="D20" s="15" t="s">
-        <v>25</v>
+      <c r="B20" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C20" s="3">
+        <v>10</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>16</v>
+        <v>13</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>13</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="I20" s="9">
-        <v>46029</v>
+        <v>46116</v>
       </c>
       <c r="J20" s="5" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B21" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="C21" s="6">
-        <v>1</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G21" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I21" s="9">
-        <v>46029</v>
-      </c>
-      <c r="J21" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B22" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="C22" s="6">
-        <v>1</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G22" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I22" s="9">
-        <v>46029</v>
-      </c>
-      <c r="J22" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C23" s="3">
-        <v>10</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G23" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I23" s="9">
-        <v>46029</v>
-      </c>
-      <c r="J23" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C24" s="3">
-        <v>1</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G24" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I24" s="9">
-        <v>46029</v>
-      </c>
-      <c r="J24" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C25" s="3">
-        <v>10</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G25" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I25" s="9">
-        <v>46029</v>
-      </c>
-      <c r="J25" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C26" s="3">
-        <v>10</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G26" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I26" s="9">
-        <v>46059</v>
-      </c>
-      <c r="J26" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C27" s="3">
-        <v>10</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G27" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I27" s="9">
-        <v>46029</v>
-      </c>
-      <c r="J27" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="C28" s="3">
-        <v>10</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G28" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I28" s="9">
-        <v>46029</v>
-      </c>
-      <c r="J28" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C29" s="3">
-        <v>10</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G29" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I29" s="9">
-        <v>46029</v>
-      </c>
-      <c r="J29" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="B30" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="C30" s="6">
-        <v>1</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G30" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H30" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I30" s="9">
-        <v>46059</v>
-      </c>
-      <c r="J30" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="1048507" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1048508" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1048489" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1048490" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -1721,10 +1322,10 @@
         <v>45474</v>
       </c>
       <c r="B2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" t="s">
         <v>29</v>
-      </c>
-      <c r="C2" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1735,7 +1336,7 @@
         <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -1743,10 +1344,10 @@
         <v>45611</v>
       </c>
       <c r="B4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -1768,7 +1369,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B1" s="10" t="s">
         <v>5</v>
@@ -1777,29 +1378,29 @@
         <v>0</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B2" t="s">
         <v>35</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>36</v>
-      </c>
-      <c r="C2" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C3" t="s">
         <v>38</v>
-      </c>
-      <c r="B3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C3" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -1807,10 +1408,10 @@
         <v>21</v>
       </c>
       <c r="B4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1818,10 +1419,10 @@
         <v>22</v>
       </c>
       <c r="B5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1829,32 +1430,32 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1862,21 +1463,21 @@
         <v>2</v>
       </c>
       <c r="B9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9" t="s">
         <v>45</v>
-      </c>
-      <c r="C9" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1884,10 +1485,10 @@
         <v>15</v>
       </c>
       <c r="B11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1895,32 +1496,32 @@
         <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C12" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B13" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C13" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>50</v>
+      </c>
+      <c r="B14" t="s">
+        <v>44</v>
+      </c>
+      <c r="C14" t="s">
         <v>51</v>
-      </c>
-      <c r="B14" t="s">
-        <v>45</v>
-      </c>
-      <c r="C14" t="s">
-        <v>52</v>
       </c>
     </row>
   </sheetData>
